--- a/data/processed/positivacao/2021-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2021-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24451,7 +24451,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B928" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr"/>
@@ -64825,7 +64825,7 @@
     <row r="2482">
       <c r="A2482" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2482" t="inlineStr"/>
@@ -66496,12 +66496,12 @@
       <c r="A2547" t="inlineStr"/>
       <c r="B2547" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 51 cliente(s), não positivou 778 cliente(s) - Total vendido: R$ 54.387,26
-Vendedor 3 - FERNANDA: positivou 84 cliente(s), não positivou 360 cliente(s) - Total vendido: R$ 47.560,32
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 652 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 84 cliente(s), não positivou 360 cliente(s) - Total vendido: R$ 47.560,32
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 652 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 455 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2547" t="inlineStr"/>
